--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -460,22 +460,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.82135</v>
+        <v>16.8238</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68667</v>
+        <v>16.64374</v>
       </c>
       <c r="E2" t="n">
-        <v>16.40814</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.53098</v>
+        <v>16.72025</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05109</v>
+        <v>0.05134</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80579</v>
+        <v>1.81162</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73599</v>
+        <v>16.91242</v>
       </c>
       <c r="D3" t="n">
-        <v>16.99456</v>
+        <v>16.43803</v>
       </c>
       <c r="E3" t="n">
-        <v>16.73121</v>
+        <v>16.84911</v>
       </c>
       <c r="F3" t="n">
-        <v>43.23556</v>
+        <v>42.24749</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05102</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78597</v>
+        <v>1.83502</v>
       </c>
     </row>
     <row r="4">
@@ -509,23 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16.87192</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>16.3059</v>
+        <v>16.62042</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58795</v>
+        <v>16.68721</v>
       </c>
       <c r="F4" t="n">
-        <v>42.24761</v>
+        <v>42.4408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05116</v>
+        <v>0.05022</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78518</v>
+        <v>1.80974</v>
       </c>
     </row>
     <row r="5">
@@ -534,23 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>16.81186</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>16.26867</v>
+        <v>16.61176</v>
       </c>
       <c r="E5" t="n">
-        <v>16.65239</v>
+        <v>16.67004</v>
       </c>
       <c r="F5" t="n">
-        <v>43.46744</v>
+        <v>41.87633</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04973</v>
+        <v>0.05101</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80804</v>
+        <v>1.82824</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +560,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.8098</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.70421</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.78303</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.54143</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.2413</v>
+        <v>17.01518</v>
       </c>
       <c r="D7" t="n">
-        <v>16.18772</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.75511</v>
+        <v>16.66796</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>42.5177</v>
+        <v>41.52475</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0497</v>
+        <v>0.05015</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82615</v>
+        <v>1.80277</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.54019</v>
+        <v>17.03135</v>
       </c>
       <c r="D8" t="n">
-        <v>16.61436</v>
+        <v>16.56035</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78465</v>
+        <v>16.97429</v>
       </c>
       <c r="F8" t="n">
-        <v>42.36015</v>
+        <v>42.81882</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05088</v>
+        <v>0.05225</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79783</v>
+        <v>1.81827</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.79898</v>
+        <v>16.74887</v>
       </c>
       <c r="D9" t="n">
-        <v>16.71869</v>
+        <v>16.44652</v>
       </c>
       <c r="E9" t="n">
-        <v>16.56432</v>
+        <v>16.6048</v>
       </c>
       <c r="F9" t="n">
-        <v>42.8168</v>
+        <v>42.35576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05045</v>
+        <v>0.05065</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84606</v>
+        <v>1.81499</v>
       </c>
     </row>
     <row r="10">
@@ -647,48 +663,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.27646</v>
+        <v>17.04476</v>
       </c>
       <c r="D10" t="n">
-        <v>16.1234</v>
+        <v>16.48391</v>
       </c>
       <c r="E10" t="n">
-        <v>16.62847</v>
+        <v>16.74086</v>
       </c>
       <c r="F10" t="n">
-        <v>41.6152</v>
+        <v>43.32666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05008</v>
+        <v>0.04971</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85912</v>
+        <v>1.79728</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +701,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.69589</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>15.90786</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.28974</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.30309</v>
-      </c>
-      <c r="G12" t="n">
-        <v>34.06114</v>
+        <v>1.11138</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.07044</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>15.63929</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.25622</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21.8944</v>
-      </c>
-      <c r="G13" t="n">
-        <v>33.61631</v>
+        <v>1.11655</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +730,11 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.93734</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>16.07824</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.73715</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22.07389</v>
-      </c>
-      <c r="G14" t="n">
-        <v>34.72876</v>
+        <v>1.12223</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +744,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.81568</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>15.96413</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.12138</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.6317</v>
-      </c>
-      <c r="G15" t="n">
-        <v>34.45067</v>
+        <v>1.10961</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +757,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.71137</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>15.60431</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.26349</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21.35299</v>
-      </c>
-      <c r="G16" t="n">
-        <v>33.92806</v>
+        <v>1.12217</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +770,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.76189</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15.76139</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.02838</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21.40551</v>
-      </c>
-      <c r="G17" t="n">
-        <v>34.15666</v>
+        <v>1.10255</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +783,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.88469</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15.78997</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.29928</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22.44456</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34.41723</v>
+        <v>1.10948</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +796,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.53474</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.80655</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.27428</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20.99651</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.18485</v>
+        <v>1.11896</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +809,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.9057</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16.02183</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.42919</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.56943</v>
-      </c>
-      <c r="G20" t="n">
-        <v>33.85303</v>
+        <v>1.12612</v>
       </c>
     </row>
   </sheetData>
